--- a/34th_Backgammon-championships_5b_output.xlsx
+++ b/34th_Backgammon-championships_5b_output.xlsx
@@ -1097,7 +1097,7 @@
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1290,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>9</v>
@@ -1302,7 +1302,7 @@
         <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>7</v>
@@ -1369,7 +1369,7 @@
         <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1415,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
@@ -1443,7 +1443,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>9</v>
